--- a/research_materials/03_results/main_results.xlsx
+++ b/research_materials/03_results/main_results.xlsx
@@ -462,7 +462,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Built: 2026-10-06 23:35 by src/build_research_materials.py</t>
+          <t>Built: 2026-10-07 02:02 by src/build_research_materials.py</t>
         </is>
       </c>
     </row>
@@ -1783,41 +1783,77 @@
       <c r="E9" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="3" t="n"/>
+      <c r="F9" s="3" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0.597</v>
+      </c>
       <c r="I9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="3" t="n"/>
-      <c r="L9" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.346</v>
+      </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="3" t="n"/>
-      <c r="O9" s="3" t="n"/>
-      <c r="P9" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N9" s="3" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="O9" s="3" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="P9" s="3" t="n">
+        <v>0.362</v>
+      </c>
       <c r="Q9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R9" s="3" t="n"/>
-      <c r="S9" s="3" t="n"/>
-      <c r="T9" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>0.389</v>
+      </c>
       <c r="U9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3" t="n"/>
-      <c r="W9" s="3" t="n"/>
-      <c r="X9" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>0.415</v>
+      </c>
       <c r="Y9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="3" t="n"/>
-      <c r="AA9" s="3" t="n"/>
-      <c r="AB9" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="AA9" s="3" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="AB9" s="3" t="n">
+        <v>0.09</v>
+      </c>
       <c r="AC9" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD9" s="3" t="n">
         <v>0.413</v>
@@ -2327,41 +2363,77 @@
       <c r="E13" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F13" s="3" t="n"/>
-      <c r="G13" s="3" t="n"/>
-      <c r="H13" s="3" t="n"/>
+      <c r="F13" s="3" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>0.586</v>
+      </c>
       <c r="I13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J13" s="3" t="n"/>
-      <c r="K13" s="3" t="n"/>
-      <c r="L13" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>0.333</v>
+      </c>
       <c r="M13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="3" t="n"/>
-      <c r="O13" s="3" t="n"/>
-      <c r="P13" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="N13" s="3" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="O13" s="3" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="P13" s="3" t="n">
+        <v>0.363</v>
+      </c>
       <c r="Q13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R13" s="3" t="n"/>
-      <c r="S13" s="3" t="n"/>
-      <c r="T13" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="S13" s="3" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="T13" s="3" t="n">
+        <v>0.407</v>
+      </c>
       <c r="U13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" s="3" t="n"/>
-      <c r="W13" s="3" t="n"/>
-      <c r="X13" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V13" s="3" t="n">
+        <v>0.378</v>
+      </c>
+      <c r="W13" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X13" s="3" t="n">
+        <v>0.408</v>
+      </c>
       <c r="Y13" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" s="3" t="n"/>
-      <c r="AA13" s="3" t="n"/>
-      <c r="AB13" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z13" s="3" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="AA13" s="3" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AB13" s="3" t="n">
+        <v>0.091</v>
+      </c>
       <c r="AC13" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD13" s="3" t="n">
         <v>0.412</v>
@@ -2436,41 +2508,77 @@
       <c r="E14" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
+      <c r="F14" s="3" t="n">
+        <v>0.645</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0.612</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0.676</v>
+      </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0.456</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="M14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="n"/>
-      <c r="O14" s="3" t="n"/>
-      <c r="P14" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>0.44</v>
+      </c>
       <c r="Q14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="n"/>
-      <c r="S14" s="3" t="n"/>
-      <c r="T14" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>0.575</v>
+      </c>
       <c r="U14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="n"/>
-      <c r="W14" s="3" t="n"/>
-      <c r="X14" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>0.57</v>
+      </c>
       <c r="Y14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="n"/>
-      <c r="AA14" s="3" t="n"/>
-      <c r="AB14" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>0.106</v>
+      </c>
+      <c r="AA14" s="3" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="AB14" s="3" t="n">
+        <v>0.127</v>
+      </c>
       <c r="AC14" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD14" s="3" t="n">
         <v>0.265</v>
@@ -2545,41 +2653,77 @@
       <c r="E15" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
+      <c r="F15" s="3" t="n">
+        <v>0.606</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0.576</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0.634</v>
+      </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>0.384</v>
+      </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3" t="n"/>
-      <c r="O15" s="3" t="n"/>
-      <c r="P15" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>0.33</v>
+      </c>
       <c r="Q15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3" t="n"/>
-      <c r="S15" s="3" t="n"/>
-      <c r="T15" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="T15" s="3" t="n">
+        <v>0.437</v>
+      </c>
       <c r="U15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="3" t="n"/>
-      <c r="W15" s="3" t="n"/>
-      <c r="X15" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>0.449</v>
+      </c>
       <c r="Y15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="3" t="n"/>
-      <c r="AA15" s="3" t="n"/>
-      <c r="AB15" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="AA15" s="3" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="AB15" s="3" t="n">
+        <v>0.075</v>
+      </c>
       <c r="AC15" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD15" s="3" t="n">
         <v>0.45</v>
@@ -3639,41 +3783,77 @@
       <c r="E23" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F23" s="3" t="n"/>
-      <c r="G23" s="3" t="n"/>
-      <c r="H23" s="3" t="n"/>
+      <c r="F23" s="3" t="n">
+        <v>0.702</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>0.734</v>
+      </c>
       <c r="I23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J23" s="3" t="n"/>
-      <c r="K23" s="3" t="n"/>
-      <c r="L23" s="3" t="n"/>
+        <v>498</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>0.61</v>
+      </c>
       <c r="M23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="3" t="n"/>
-      <c r="O23" s="3" t="n"/>
-      <c r="P23" s="3" t="n"/>
+        <v>498</v>
+      </c>
+      <c r="N23" s="3" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="O23" s="3" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="P23" s="3" t="n">
+        <v>0.231</v>
+      </c>
       <c r="Q23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R23" s="3" t="n"/>
-      <c r="S23" s="3" t="n"/>
-      <c r="T23" s="3" t="n"/>
+        <v>498</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="S23" s="3" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="T23" s="3" t="n">
+        <v>0.588</v>
+      </c>
       <c r="U23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" s="3" t="n"/>
-      <c r="W23" s="3" t="n"/>
-      <c r="X23" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V23" s="3" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="W23" s="3" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="X23" s="3" t="n">
+        <v>0.605</v>
+      </c>
       <c r="Y23" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z23" s="3" t="n"/>
-      <c r="AA23" s="3" t="n"/>
-      <c r="AB23" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z23" s="3" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="AA23" s="3" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="AB23" s="3" t="n">
+        <v>0.08500000000000001</v>
+      </c>
       <c r="AC23" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD23" s="3" t="n">
         <v>0.177</v>
@@ -3748,41 +3928,77 @@
       <c r="E24" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F24" s="3" t="n"/>
-      <c r="G24" s="3" t="n"/>
-      <c r="H24" s="3" t="n"/>
+      <c r="F24" s="3" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>0.573</v>
+      </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="3" t="n"/>
-      <c r="K24" s="3" t="n"/>
-      <c r="L24" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>0.296</v>
+      </c>
       <c r="M24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="3" t="n"/>
-      <c r="O24" s="3" t="n"/>
-      <c r="P24" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N24" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O24" s="3" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="P24" s="3" t="n">
+        <v>0.394</v>
+      </c>
       <c r="Q24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R24" s="3" t="n"/>
-      <c r="S24" s="3" t="n"/>
-      <c r="T24" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>0.346</v>
+      </c>
       <c r="U24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3" t="n"/>
-      <c r="W24" s="3" t="n"/>
-      <c r="X24" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="W24" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>0.389</v>
+      </c>
       <c r="Y24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="3" t="n"/>
-      <c r="AA24" s="3" t="n"/>
-      <c r="AB24" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z24" s="3" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="AA24" s="3" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="AB24" s="3" t="n">
+        <v>0.09</v>
+      </c>
       <c r="AC24" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD24" s="3" t="n">
         <v>0.29</v>
@@ -3857,41 +4073,77 @@
       <c r="E25" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
+      <c r="F25" s="3" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>0.488</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>0.544</v>
+      </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>0.252</v>
+      </c>
       <c r="M25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="3" t="n"/>
-      <c r="O25" s="3" t="n"/>
-      <c r="P25" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>0.372</v>
+      </c>
       <c r="Q25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="3" t="n"/>
-      <c r="S25" s="3" t="n"/>
-      <c r="T25" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>0.359</v>
+      </c>
       <c r="U25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="3" t="n"/>
-      <c r="W25" s="3" t="n"/>
-      <c r="X25" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>0.375</v>
+      </c>
       <c r="Y25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="3" t="n"/>
-      <c r="AA25" s="3" t="n"/>
-      <c r="AB25" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="AA25" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB25" s="3" t="n">
+        <v>0.08400000000000001</v>
+      </c>
       <c r="AC25" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD25" s="3" t="n">
         <v>0.391</v>
@@ -4401,41 +4653,77 @@
       <c r="E29" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F29" s="3" t="n"/>
-      <c r="G29" s="3" t="n"/>
-      <c r="H29" s="3" t="n"/>
+      <c r="F29" s="3" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>0.578</v>
+      </c>
       <c r="I29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3" t="n"/>
-      <c r="K29" s="3" t="n"/>
-      <c r="L29" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>0.318</v>
+      </c>
       <c r="M29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3" t="n"/>
-      <c r="O29" s="3" t="n"/>
-      <c r="P29" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N29" s="3" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="O29" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P29" s="3" t="n">
+        <v>0.354</v>
+      </c>
       <c r="Q29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3" t="n"/>
-      <c r="S29" s="3" t="n"/>
-      <c r="T29" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="S29" s="3" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="T29" s="3" t="n">
+        <v>0.387</v>
+      </c>
       <c r="U29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3" t="n"/>
-      <c r="W29" s="3" t="n"/>
-      <c r="X29" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V29" s="3" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="W29" s="3" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="X29" s="3" t="n">
+        <v>0.396</v>
+      </c>
       <c r="Y29" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="n"/>
-      <c r="AA29" s="3" t="n"/>
-      <c r="AB29" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z29" s="3" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="AA29" s="3" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="AB29" s="3" t="n">
+        <v>0.076</v>
+      </c>
       <c r="AC29" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD29" s="3" t="n">
         <v>0.407</v>
@@ -4510,41 +4798,77 @@
       <c r="E30" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F30" s="3" t="n"/>
-      <c r="G30" s="3" t="n"/>
-      <c r="H30" s="3" t="n"/>
+      <c r="F30" s="3" t="n">
+        <v>0.6909999999999999</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0.655</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>0.724</v>
+      </c>
       <c r="I30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J30" s="3" t="n"/>
-      <c r="K30" s="3" t="n"/>
-      <c r="L30" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>0.602</v>
+      </c>
       <c r="M30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="3" t="n"/>
-      <c r="O30" s="3" t="n"/>
-      <c r="P30" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N30" s="3" t="n">
+        <v>0.232</v>
+      </c>
+      <c r="O30" s="3" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="P30" s="3" t="n">
+        <v>0.27</v>
+      </c>
       <c r="Q30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R30" s="3" t="n"/>
-      <c r="S30" s="3" t="n"/>
-      <c r="T30" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="S30" s="3" t="n">
+        <v>0.513</v>
+      </c>
+      <c r="T30" s="3" t="n">
+        <v>0.577</v>
+      </c>
       <c r="U30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" s="3" t="n"/>
-      <c r="W30" s="3" t="n"/>
-      <c r="X30" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V30" s="3" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="W30" s="3" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="X30" s="3" t="n">
+        <v>0.57</v>
+      </c>
       <c r="Y30" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="3" t="n"/>
-      <c r="AA30" s="3" t="n"/>
-      <c r="AB30" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z30" s="3" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="AA30" s="3" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="AB30" s="3" t="n">
+        <v>0.079</v>
+      </c>
       <c r="AC30" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD30" s="3" t="n">
         <v>0.188</v>
@@ -4619,41 +4943,77 @@
       <c r="E31" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
+      <c r="F31" s="3" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0.534</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>0.592</v>
+      </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="n"/>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>0.336</v>
+      </c>
       <c r="M31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="3" t="n"/>
-      <c r="O31" s="3" t="n"/>
-      <c r="P31" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>0.354</v>
+      </c>
       <c r="Q31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="3" t="n"/>
-      <c r="S31" s="3" t="n"/>
-      <c r="T31" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>0.412</v>
+      </c>
       <c r="U31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="3" t="n"/>
-      <c r="W31" s="3" t="n"/>
-      <c r="X31" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>0.431</v>
+      </c>
       <c r="Y31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="3" t="n"/>
-      <c r="AA31" s="3" t="n"/>
-      <c r="AB31" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="AA31" s="3" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AB31" s="3" t="n">
+        <v>0.079</v>
+      </c>
       <c r="AC31" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD31" s="3" t="n">
         <v>0.441</v>
@@ -5858,41 +6218,77 @@
       <c r="E40" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F40" s="3" t="n"/>
-      <c r="G40" s="3" t="n"/>
-      <c r="H40" s="3" t="n"/>
+      <c r="F40" s="3" t="n">
+        <v>0.574</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>0.604</v>
+      </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J40" s="3" t="n"/>
-      <c r="K40" s="3" t="n"/>
-      <c r="L40" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>0.349</v>
+      </c>
       <c r="M40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="3" t="n"/>
-      <c r="O40" s="3" t="n"/>
-      <c r="P40" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="N40" s="3" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="O40" s="3" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="P40" s="3" t="n">
+        <v>0.411</v>
+      </c>
       <c r="Q40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" s="3" t="n"/>
-      <c r="S40" s="3" t="n"/>
-      <c r="T40" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="S40" s="3" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="T40" s="3" t="n">
+        <v>0.452</v>
+      </c>
       <c r="U40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" s="3" t="n"/>
-      <c r="W40" s="3" t="n"/>
-      <c r="X40" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V40" s="3" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="W40" s="3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="X40" s="3" t="n">
+        <v>0.445</v>
+      </c>
       <c r="Y40" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z40" s="3" t="n"/>
-      <c r="AA40" s="3" t="n"/>
-      <c r="AB40" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z40" s="3" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AA40" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="AB40" s="3" t="n">
+        <v>0.073</v>
+      </c>
       <c r="AC40" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD40" s="3" t="n">
         <v>0.446</v>
@@ -5967,41 +6363,77 @@
       <c r="E41" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F41" s="3" t="n"/>
-      <c r="G41" s="3" t="n"/>
-      <c r="H41" s="3" t="n"/>
+      <c r="F41" s="3" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0.834</v>
+      </c>
       <c r="I41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="3" t="n"/>
-      <c r="K41" s="3" t="n"/>
-      <c r="L41" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0.626</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>0.71</v>
+      </c>
       <c r="M41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="3" t="n"/>
-      <c r="O41" s="3" t="n"/>
-      <c r="P41" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N41" s="3" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="O41" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="P41" s="3" t="n">
+        <v>0.216</v>
+      </c>
       <c r="Q41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R41" s="3" t="n"/>
-      <c r="S41" s="3" t="n"/>
-      <c r="T41" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="S41" s="3" t="n">
+        <v>0.636</v>
+      </c>
+      <c r="T41" s="3" t="n">
+        <v>0.702</v>
+      </c>
       <c r="U41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V41" s="3" t="n"/>
-      <c r="W41" s="3" t="n"/>
-      <c r="X41" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V41" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="W41" s="3" t="n">
+        <v>0.638</v>
+      </c>
+      <c r="X41" s="3" t="n">
+        <v>0.702</v>
+      </c>
       <c r="Y41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z41" s="3" t="n"/>
-      <c r="AA41" s="3" t="n"/>
-      <c r="AB41" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z41" s="3" t="n">
+        <v>0.017</v>
+      </c>
+      <c r="AA41" s="3" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AB41" s="3" t="n">
+        <v>0.024</v>
+      </c>
       <c r="AC41" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD41" s="3" t="n">
         <v>0.731</v>
@@ -6511,41 +6943,77 @@
       <c r="E45" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F45" s="3" t="n"/>
-      <c r="G45" s="3" t="n"/>
-      <c r="H45" s="3" t="n"/>
+      <c r="F45" s="3" t="n">
+        <v>0.5639999999999999</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>0.594</v>
+      </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="3" t="n"/>
-      <c r="K45" s="3" t="n"/>
-      <c r="L45" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>0.338</v>
+      </c>
       <c r="M45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="3" t="n"/>
-      <c r="O45" s="3" t="n"/>
-      <c r="P45" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N45" s="3" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="O45" s="3" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="P45" s="3" t="n">
+        <v>0.384</v>
+      </c>
       <c r="Q45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R45" s="3" t="n"/>
-      <c r="S45" s="3" t="n"/>
-      <c r="T45" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>0.415</v>
+      </c>
       <c r="U45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" s="3" t="n"/>
-      <c r="W45" s="3" t="n"/>
-      <c r="X45" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>0.438</v>
+      </c>
       <c r="Y45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" s="3" t="n"/>
-      <c r="AA45" s="3" t="n"/>
-      <c r="AB45" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="AA45" s="3" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="AB45" s="3" t="n">
+        <v>0.08</v>
+      </c>
       <c r="AC45" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD45" s="3" t="n">
         <v>0.436</v>
@@ -6620,41 +7088,77 @@
       <c r="E46" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F46" s="3" t="n"/>
-      <c r="G46" s="3" t="n"/>
-      <c r="H46" s="3" t="n"/>
+      <c r="F46" s="3" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>0.588</v>
+      </c>
       <c r="I46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="3" t="n"/>
-      <c r="K46" s="3" t="n"/>
-      <c r="L46" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>0.393</v>
+      </c>
       <c r="M46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="3" t="n"/>
-      <c r="O46" s="3" t="n"/>
-      <c r="P46" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="N46" s="3" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="O46" s="3" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="P46" s="3" t="n">
+        <v>0.477</v>
+      </c>
       <c r="Q46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R46" s="3" t="n"/>
-      <c r="S46" s="3" t="n"/>
-      <c r="T46" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="S46" s="3" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="T46" s="3" t="n">
+        <v>0.547</v>
+      </c>
       <c r="U46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V46" s="3" t="n"/>
-      <c r="W46" s="3" t="n"/>
-      <c r="X46" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V46" s="3" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="W46" s="3" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="X46" s="3" t="n">
+        <v>0.546</v>
+      </c>
       <c r="Y46" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z46" s="3" t="n"/>
-      <c r="AA46" s="3" t="n"/>
-      <c r="AB46" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z46" s="3" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AA46" s="3" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="AB46" s="3" t="n">
+        <v>0.105</v>
+      </c>
       <c r="AC46" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD46" s="3" t="n">
         <v>0.192</v>
@@ -6729,41 +7233,77 @@
       <c r="E47" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F47" s="3" t="n"/>
-      <c r="G47" s="3" t="n"/>
-      <c r="H47" s="3" t="n"/>
+      <c r="F47" s="3" t="n">
+        <v>0.639</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0.608</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>0.67</v>
+      </c>
       <c r="I47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3" t="n"/>
-      <c r="K47" s="3" t="n"/>
-      <c r="L47" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>0.46</v>
+      </c>
       <c r="M47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="3" t="n"/>
-      <c r="O47" s="3" t="n"/>
-      <c r="P47" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N47" s="3" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="O47" s="3" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="P47" s="3" t="n">
+        <v>0.356</v>
+      </c>
       <c r="Q47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R47" s="3" t="n"/>
-      <c r="S47" s="3" t="n"/>
-      <c r="T47" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>0.465</v>
+      </c>
+      <c r="S47" s="3" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="T47" s="3" t="n">
+        <v>0.499</v>
+      </c>
       <c r="U47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V47" s="3" t="n"/>
-      <c r="W47" s="3" t="n"/>
-      <c r="X47" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V47" s="3" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="W47" s="3" t="n">
+        <v>0.457</v>
+      </c>
+      <c r="X47" s="3" t="n">
+        <v>0.522</v>
+      </c>
       <c r="Y47" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z47" s="3" t="n"/>
-      <c r="AA47" s="3" t="n"/>
-      <c r="AB47" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z47" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AA47" s="3" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AB47" s="3" t="n">
+        <v>0.075</v>
+      </c>
       <c r="AC47" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD47" s="3" t="n">
         <v>0.51</v>
@@ -8286,41 +8826,77 @@
       <c r="E10" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
+      <c r="F10" s="3" t="n">
+        <v>0.5659999999999999</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0.609</v>
+      </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0.384</v>
+      </c>
       <c r="M10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
-      <c r="P10" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>0.208</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0.308</v>
+      </c>
       <c r="Q10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="3" t="n"/>
-      <c r="S10" s="3" t="n"/>
-      <c r="T10" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>0.369</v>
+      </c>
       <c r="U10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="n"/>
-      <c r="W10" s="3" t="n"/>
-      <c r="X10" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>0.389</v>
+      </c>
       <c r="Y10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="3" t="n"/>
-      <c r="AA10" s="3" t="n"/>
-      <c r="AB10" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="AA10" s="3" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="AB10" s="3" t="n">
+        <v>0.115</v>
+      </c>
       <c r="AC10" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="AD10" s="3" t="n">
         <v>0.311</v>
@@ -8830,41 +9406,77 @@
       <c r="E14" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
+      <c r="F14" s="3" t="n">
+        <v>0.543</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0.582</v>
+      </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0.33</v>
+      </c>
       <c r="M14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="n"/>
-      <c r="O14" s="3" t="n"/>
-      <c r="P14" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>0.33</v>
+      </c>
       <c r="Q14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="n"/>
-      <c r="S14" s="3" t="n"/>
-      <c r="T14" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>0.385</v>
+      </c>
       <c r="U14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="n"/>
-      <c r="W14" s="3" t="n"/>
-      <c r="X14" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>0.417</v>
+      </c>
       <c r="Y14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="n"/>
-      <c r="AA14" s="3" t="n"/>
-      <c r="AB14" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AA14" s="3" t="n">
+        <v>0.063</v>
+      </c>
+      <c r="AB14" s="3" t="n">
+        <v>0.115</v>
+      </c>
       <c r="AC14" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="AD14" s="3" t="n">
         <v>0.323</v>
@@ -8939,41 +9551,77 @@
       <c r="E15" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
+      <c r="F15" s="3" t="n">
+        <v>0.658</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0.617</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0.696</v>
+      </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
+        <v>278</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0.453</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0.396</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>0.511</v>
+      </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3" t="n"/>
-      <c r="O15" s="3" t="n"/>
-      <c r="P15" s="3" t="n"/>
+        <v>278</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>0.403</v>
+      </c>
       <c r="Q15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3" t="n"/>
-      <c r="S15" s="3" t="n"/>
-      <c r="T15" s="3" t="n"/>
+        <v>278</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="T15" s="3" t="n">
+        <v>0.553</v>
+      </c>
       <c r="U15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="3" t="n"/>
-      <c r="W15" s="3" t="n"/>
-      <c r="X15" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>0.511</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>0.466</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>0.555</v>
+      </c>
       <c r="Y15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="3" t="n"/>
-      <c r="AA15" s="3" t="n"/>
-      <c r="AB15" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <v>0.111</v>
+      </c>
+      <c r="AA15" s="3" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="AB15" s="3" t="n">
+        <v>0.142</v>
+      </c>
       <c r="AC15" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="AD15" s="3" t="n">
         <v>0.216</v>
@@ -9048,41 +9696,77 @@
       <c r="E16" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
+      <c r="F16" s="3" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0.638</v>
+      </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>0.394</v>
+      </c>
       <c r="M16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="3" t="n"/>
-      <c r="O16" s="3" t="n"/>
-      <c r="P16" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>0.33</v>
+      </c>
       <c r="Q16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="3" t="n"/>
-      <c r="S16" s="3" t="n"/>
-      <c r="T16" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>0.4</v>
+      </c>
       <c r="U16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="3" t="n"/>
-      <c r="W16" s="3" t="n"/>
-      <c r="X16" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="V16" s="3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>0.413</v>
+      </c>
       <c r="Y16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="3" t="n"/>
-      <c r="AA16" s="3" t="n"/>
-      <c r="AB16" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Z16" s="3" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="AA16" s="3" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB16" s="3" t="n">
+        <v>0.122</v>
+      </c>
       <c r="AC16" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="AD16" s="3" t="n">
         <v>0.349</v>
@@ -10317,41 +11001,77 @@
       <c r="E25" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
+      <c r="F25" s="3" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>0.643</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>0.731</v>
+      </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>0.595</v>
+      </c>
       <c r="M25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="3" t="n"/>
-      <c r="O25" s="3" t="n"/>
-      <c r="P25" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>0.115</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>0.204</v>
+      </c>
       <c r="Q25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="3" t="n"/>
-      <c r="S25" s="3" t="n"/>
-      <c r="T25" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>0.59</v>
+      </c>
       <c r="U25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="3" t="n"/>
-      <c r="W25" s="3" t="n"/>
-      <c r="X25" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>0.536</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>0.576</v>
+      </c>
       <c r="Y25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="3" t="n"/>
-      <c r="AA25" s="3" t="n"/>
-      <c r="AB25" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="AA25" s="3" t="n">
+        <v>0.036</v>
+      </c>
+      <c r="AB25" s="3" t="n">
+        <v>0.07099999999999999</v>
+      </c>
       <c r="AC25" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="AD25" s="3" t="n">
         <v>0.154</v>
@@ -10426,41 +11146,77 @@
       <c r="E26" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
-      <c r="H26" s="3" t="n"/>
+      <c r="F26" s="3" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>0.625</v>
+      </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>0.38</v>
+      </c>
       <c r="M26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3" t="n"/>
-      <c r="O26" s="3" t="n"/>
-      <c r="P26" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>0.211</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>0.265</v>
+      </c>
       <c r="Q26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="3" t="n"/>
-      <c r="S26" s="3" t="n"/>
-      <c r="T26" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>0.337</v>
+      </c>
       <c r="U26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="3" t="n"/>
-      <c r="W26" s="3" t="n"/>
-      <c r="X26" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>0.364</v>
+      </c>
       <c r="Y26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="3" t="n"/>
-      <c r="AA26" s="3" t="n"/>
-      <c r="AB26" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="AA26" s="3" t="n">
+        <v>0.057</v>
+      </c>
+      <c r="AB26" s="3" t="n">
+        <v>0.102</v>
+      </c>
       <c r="AC26" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="AD26" s="3" t="n">
         <v>0.248</v>
@@ -10535,41 +11291,77 @@
       <c r="E27" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
+      <c r="F27" s="3" t="n">
+        <v>0.547</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>0.586</v>
+      </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>0.323</v>
+      </c>
       <c r="M27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3" t="n"/>
-      <c r="O27" s="3" t="n"/>
-      <c r="P27" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>0.197</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>0.297</v>
+      </c>
       <c r="Q27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="3" t="n"/>
-      <c r="S27" s="3" t="n"/>
-      <c r="T27" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>0.353</v>
+      </c>
       <c r="U27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="3" t="n"/>
-      <c r="W27" s="3" t="n"/>
-      <c r="X27" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="X27" s="3" t="n">
+        <v>0.381</v>
+      </c>
       <c r="Y27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="3" t="n"/>
-      <c r="AA27" s="3" t="n"/>
-      <c r="AB27" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AA27" s="3" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="AB27" s="3" t="n">
+        <v>0.113</v>
+      </c>
       <c r="AC27" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="AD27" s="3" t="n">
         <v>0.297</v>
@@ -11079,41 +11871,77 @@
       <c r="E31" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
+      <c r="F31" s="3" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>0.597</v>
+      </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="n"/>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0.247</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>0.351</v>
+      </c>
       <c r="M31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="3" t="n"/>
-      <c r="O31" s="3" t="n"/>
-      <c r="P31" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>0.362</v>
+      </c>
       <c r="Q31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="3" t="n"/>
-      <c r="S31" s="3" t="n"/>
-      <c r="T31" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>0.377</v>
+      </c>
       <c r="U31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="3" t="n"/>
-      <c r="W31" s="3" t="n"/>
-      <c r="X31" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>0.413</v>
+      </c>
       <c r="Y31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="3" t="n"/>
-      <c r="AA31" s="3" t="n"/>
-      <c r="AB31" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="AA31" s="3" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="AB31" s="3" t="n">
+        <v>0.128</v>
+      </c>
       <c r="AC31" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="AD31" s="3" t="n">
         <v>0.329</v>
@@ -11188,41 +12016,77 @@
       <c r="E32" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="F32" s="3" t="n"/>
-      <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3" t="n"/>
+      <c r="F32" s="3" t="n">
+        <v>0.672</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0.715</v>
+      </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="n"/>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0.534</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0.473</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>0.591</v>
+      </c>
       <c r="M32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3" t="n"/>
-      <c r="O32" s="3" t="n"/>
-      <c r="P32" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>0.161</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>0.122</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>0.208</v>
+      </c>
       <c r="Q32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3" t="n"/>
-      <c r="S32" s="3" t="n"/>
-      <c r="T32" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>0.5610000000000001</v>
+      </c>
       <c r="U32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3" t="n"/>
-      <c r="W32" s="3" t="n"/>
-      <c r="X32" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="V32" s="3" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>0.576</v>
+      </c>
       <c r="Y32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3" t="n"/>
-      <c r="AA32" s="3" t="n"/>
-      <c r="AB32" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="AA32" s="3" t="n">
+        <v>0.042</v>
+      </c>
+      <c r="AB32" s="3" t="n">
+        <v>0.083</v>
+      </c>
       <c r="AC32" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="AD32" s="3" t="n">
         <v>0.16</v>
@@ -11297,41 +12161,77 @@
       <c r="E33" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n"/>
+      <c r="F33" s="3" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>0.595</v>
+      </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="n"/>
-      <c r="K33" s="3" t="n"/>
-      <c r="L33" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>0.33</v>
+      </c>
       <c r="M33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3" t="n"/>
-      <c r="O33" s="3" t="n"/>
-      <c r="P33" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>0.351</v>
+      </c>
       <c r="Q33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="3" t="n"/>
-      <c r="S33" s="3" t="n"/>
-      <c r="T33" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>0.39</v>
+      </c>
       <c r="U33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="3" t="n"/>
-      <c r="W33" s="3" t="n"/>
-      <c r="X33" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="W33" s="3" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>0.393</v>
+      </c>
       <c r="Y33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="3" t="n"/>
-      <c r="AA33" s="3" t="n"/>
-      <c r="AB33" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Z33" s="3" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="AA33" s="3" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="AB33" s="3" t="n">
+        <v>0.097</v>
+      </c>
       <c r="AC33" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="AD33" s="3" t="n">
         <v>0.338</v>
@@ -12711,41 +13611,77 @@
       <c r="E43" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="F43" s="3" t="n"/>
-      <c r="G43" s="3" t="n"/>
-      <c r="H43" s="3" t="n"/>
+      <c r="F43" s="3" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>0.595</v>
+      </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="n"/>
-      <c r="K43" s="3" t="n"/>
-      <c r="L43" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>0.229</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>0.337</v>
+      </c>
       <c r="M43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3" t="n"/>
-      <c r="O43" s="3" t="n"/>
-      <c r="P43" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>0.222</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>0.33</v>
+      </c>
       <c r="Q43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="3" t="n"/>
-      <c r="S43" s="3" t="n"/>
-      <c r="T43" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>0.409</v>
+      </c>
       <c r="U43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="3" t="n"/>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>0.401</v>
+      </c>
       <c r="Y43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="3" t="n"/>
-      <c r="AA43" s="3" t="n"/>
-      <c r="AB43" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="AA43" s="3" t="n">
+        <v>0.044</v>
+      </c>
+      <c r="AB43" s="3" t="n">
+        <v>0.092</v>
+      </c>
       <c r="AC43" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="AD43" s="3" t="n">
         <v>0.326</v>
@@ -12820,41 +13756,77 @@
       <c r="E44" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="F44" s="3" t="n"/>
-      <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="n"/>
+      <c r="F44" s="3" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>0.706</v>
+      </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="n"/>
-      <c r="K44" s="3" t="n"/>
-      <c r="L44" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>0.437</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>0.498</v>
+      </c>
       <c r="M44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3" t="n"/>
-      <c r="O44" s="3" t="n"/>
-      <c r="P44" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>0.219</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>0.323</v>
+      </c>
       <c r="Q44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="3" t="n"/>
-      <c r="S44" s="3" t="n"/>
-      <c r="T44" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>0.486</v>
+      </c>
       <c r="U44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" s="3" t="n"/>
-      <c r="W44" s="3" t="n"/>
-      <c r="X44" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>0.477</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>0.52</v>
+      </c>
       <c r="Y44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="3" t="n"/>
-      <c r="AA44" s="3" t="n"/>
-      <c r="AB44" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Z44" s="3" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="AA44" s="3" t="n">
+        <v>0.043</v>
+      </c>
+      <c r="AB44" s="3" t="n">
+        <v>0.091</v>
+      </c>
       <c r="AC44" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="AD44" s="3" t="n">
         <v>0.439</v>
@@ -13364,41 +14336,77 @@
       <c r="E48" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="F48" s="3" t="n"/>
-      <c r="G48" s="3" t="n"/>
-      <c r="H48" s="3" t="n"/>
+      <c r="F48" s="3" t="n">
+        <v>0.588</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>0.629</v>
+      </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="n"/>
-      <c r="K48" s="3" t="n"/>
-      <c r="L48" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>0.384</v>
+      </c>
       <c r="M48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="3" t="n"/>
-      <c r="O48" s="3" t="n"/>
-      <c r="P48" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>0.265</v>
+      </c>
+      <c r="O48" s="3" t="n">
+        <v>0.215</v>
+      </c>
+      <c r="P48" s="3" t="n">
+        <v>0.315</v>
+      </c>
       <c r="Q48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="3" t="n"/>
-      <c r="S48" s="3" t="n"/>
-      <c r="T48" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="S48" s="3" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="T48" s="3" t="n">
+        <v>0.405</v>
+      </c>
       <c r="U48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="3" t="n"/>
-      <c r="W48" s="3" t="n"/>
-      <c r="X48" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="V48" s="3" t="n">
+        <v>0.399</v>
+      </c>
+      <c r="W48" s="3" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="X48" s="3" t="n">
+        <v>0.441</v>
+      </c>
       <c r="Y48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" s="3" t="n"/>
-      <c r="AA48" s="3" t="n"/>
-      <c r="AB48" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Z48" s="3" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="AA48" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AB48" s="3" t="n">
+        <v>0.126</v>
+      </c>
       <c r="AC48" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="AD48" s="3" t="n">
         <v>0.341</v>
@@ -13473,41 +14481,77 @@
       <c r="E49" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="F49" s="3" t="n"/>
-      <c r="G49" s="3" t="n"/>
-      <c r="H49" s="3" t="n"/>
+      <c r="F49" s="3" t="n">
+        <v>0.552</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>0.593</v>
+      </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3" t="n"/>
-      <c r="K49" s="3" t="n"/>
-      <c r="L49" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>0.366</v>
+      </c>
       <c r="M49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="3" t="n"/>
-      <c r="O49" s="3" t="n"/>
-      <c r="P49" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>0.455</v>
+      </c>
       <c r="Q49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" s="3" t="n"/>
-      <c r="S49" s="3" t="n"/>
-      <c r="T49" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>0.491</v>
+      </c>
+      <c r="S49" s="3" t="n">
+        <v>0.448</v>
+      </c>
+      <c r="T49" s="3" t="n">
+        <v>0.535</v>
+      </c>
       <c r="U49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" s="3" t="n"/>
-      <c r="W49" s="3" t="n"/>
-      <c r="X49" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="V49" s="3" t="n">
+        <v>0.472</v>
+      </c>
+      <c r="W49" s="3" t="n">
+        <v>0.429</v>
+      </c>
+      <c r="X49" s="3" t="n">
+        <v>0.515</v>
+      </c>
       <c r="Y49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" s="3" t="n"/>
-      <c r="AA49" s="3" t="n"/>
-      <c r="AB49" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Z49" s="3" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AA49" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AB49" s="3" t="n">
+        <v>0.111</v>
+      </c>
       <c r="AC49" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="AD49" s="3" t="n">
         <v>0.158</v>
@@ -13582,41 +14626,77 @@
       <c r="E50" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="F50" s="3" t="n"/>
-      <c r="G50" s="3" t="n"/>
-      <c r="H50" s="3" t="n"/>
+      <c r="F50" s="3" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>0.652</v>
+      </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="3" t="n"/>
-      <c r="K50" s="3" t="n"/>
-      <c r="L50" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>0.401</v>
+      </c>
       <c r="M50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="3" t="n"/>
-      <c r="O50" s="3" t="n"/>
-      <c r="P50" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="O50" s="3" t="n">
+        <v>0.244</v>
+      </c>
+      <c r="P50" s="3" t="n">
+        <v>0.351</v>
+      </c>
       <c r="Q50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="3" t="n"/>
-      <c r="S50" s="3" t="n"/>
-      <c r="T50" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="S50" s="3" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="T50" s="3" t="n">
+        <v>0.447</v>
+      </c>
       <c r="U50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" s="3" t="n"/>
-      <c r="W50" s="3" t="n"/>
-      <c r="X50" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="V50" s="3" t="n">
+        <v>0.407</v>
+      </c>
+      <c r="W50" s="3" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="X50" s="3" t="n">
+        <v>0.448</v>
+      </c>
       <c r="Y50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" s="3" t="n"/>
-      <c r="AA50" s="3" t="n"/>
-      <c r="AB50" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Z50" s="3" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="AA50" s="3" t="n">
+        <v>0.055</v>
+      </c>
+      <c r="AB50" s="3" t="n">
+        <v>0.107</v>
+      </c>
       <c r="AC50" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="AD50" s="3" t="n">
         <v>0.379</v>
@@ -15139,41 +16219,77 @@
       <c r="E10" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
+      <c r="F10" s="3" t="n">
+        <v>0.544</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.516</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0.573</v>
+      </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0.302</v>
+      </c>
       <c r="M10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
-      <c r="P10" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0.368</v>
+      </c>
       <c r="Q10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="3" t="n"/>
-      <c r="S10" s="3" t="n"/>
-      <c r="T10" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>0.408</v>
+      </c>
       <c r="U10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="n"/>
-      <c r="W10" s="3" t="n"/>
-      <c r="X10" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>0.408</v>
+      </c>
       <c r="Y10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="3" t="n"/>
-      <c r="AA10" s="3" t="n"/>
-      <c r="AB10" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="AA10" s="3" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="AB10" s="3" t="n">
+        <v>0.079</v>
+      </c>
       <c r="AC10" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD10" s="3" t="n">
         <v>0.377</v>
@@ -15683,41 +16799,77 @@
       <c r="E14" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
+      <c r="F14" s="3" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0.254</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0.294</v>
+      </c>
       <c r="M14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="n"/>
-      <c r="O14" s="3" t="n"/>
-      <c r="P14" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>0.35</v>
+      </c>
       <c r="Q14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="n"/>
-      <c r="S14" s="3" t="n"/>
-      <c r="T14" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>0.405</v>
+      </c>
       <c r="U14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="n"/>
-      <c r="W14" s="3" t="n"/>
-      <c r="X14" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>0.389</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>0.419</v>
+      </c>
       <c r="Y14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="n"/>
-      <c r="AA14" s="3" t="n"/>
-      <c r="AB14" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="AA14" s="3" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AB14" s="3" t="n">
+        <v>0.092</v>
+      </c>
       <c r="AC14" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD14" s="3" t="n">
         <v>0.376</v>
@@ -15792,41 +16944,77 @@
       <c r="E15" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
+      <c r="F15" s="3" t="n">
+        <v>0.664</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0.632</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0.696</v>
+      </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>0.526</v>
+      </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3" t="n"/>
-      <c r="O15" s="3" t="n"/>
-      <c r="P15" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>0.424</v>
+      </c>
       <c r="Q15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3" t="n"/>
-      <c r="S15" s="3" t="n"/>
-      <c r="T15" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="T15" s="3" t="n">
+        <v>0.595</v>
+      </c>
       <c r="U15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="3" t="n"/>
-      <c r="W15" s="3" t="n"/>
-      <c r="X15" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>0.5610000000000001</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>0.59</v>
+      </c>
       <c r="Y15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="3" t="n"/>
-      <c r="AA15" s="3" t="n"/>
-      <c r="AB15" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="AA15" s="3" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="AB15" s="3" t="n">
+        <v>0.123</v>
+      </c>
       <c r="AC15" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD15" s="3" t="n">
         <v>0.265</v>
@@ -15901,41 +17089,77 @@
       <c r="E16" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
+      <c r="F16" s="3" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0.555</v>
+      </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>0.266</v>
+      </c>
       <c r="M16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="3" t="n"/>
-      <c r="O16" s="3" t="n"/>
-      <c r="P16" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>0.402</v>
+      </c>
       <c r="Q16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="3" t="n"/>
-      <c r="S16" s="3" t="n"/>
-      <c r="T16" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>0.395</v>
+      </c>
       <c r="U16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="3" t="n"/>
-      <c r="W16" s="3" t="n"/>
-      <c r="X16" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V16" s="3" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>0.396</v>
+      </c>
       <c r="Y16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="3" t="n"/>
-      <c r="AA16" s="3" t="n"/>
-      <c r="AB16" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z16" s="3" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="AA16" s="3" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AB16" s="3" t="n">
+        <v>0.096</v>
+      </c>
       <c r="AC16" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD16" s="3" t="n">
         <v>0.361</v>
@@ -17170,41 +18394,77 @@
       <c r="E25" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
+      <c r="F25" s="3" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>0.6879999999999999</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>0.752</v>
+      </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
+        <v>497</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>0.571</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>0.616</v>
+      </c>
       <c r="M25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="3" t="n"/>
-      <c r="O25" s="3" t="n"/>
-      <c r="P25" s="3" t="n"/>
+        <v>497</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>0.235</v>
+      </c>
       <c r="Q25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="3" t="n"/>
-      <c r="S25" s="3" t="n"/>
-      <c r="T25" s="3" t="n"/>
+        <v>497</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>0.572</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>0.542</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>0.602</v>
+      </c>
       <c r="U25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="3" t="n"/>
-      <c r="W25" s="3" t="n"/>
-      <c r="X25" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>0.569</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>0.598</v>
+      </c>
       <c r="Y25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="3" t="n"/>
-      <c r="AA25" s="3" t="n"/>
-      <c r="AB25" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="AA25" s="3" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AB25" s="3" t="n">
+        <v>0.08799999999999999</v>
+      </c>
       <c r="AC25" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD25" s="3" t="n">
         <v>0.179</v>
@@ -17279,41 +18539,77 @@
       <c r="E26" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
-      <c r="H26" s="3" t="n"/>
+      <c r="F26" s="3" t="n">
+        <v>0.595</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0.5679999999999999</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>0.623</v>
+      </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>0.36</v>
+      </c>
       <c r="M26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3" t="n"/>
-      <c r="O26" s="3" t="n"/>
-      <c r="P26" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>0.326</v>
+      </c>
       <c r="Q26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="3" t="n"/>
-      <c r="S26" s="3" t="n"/>
-      <c r="T26" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>0.39</v>
+      </c>
       <c r="U26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="3" t="n"/>
-      <c r="W26" s="3" t="n"/>
-      <c r="X26" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>0.416</v>
+      </c>
       <c r="Y26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="3" t="n"/>
-      <c r="AA26" s="3" t="n"/>
-      <c r="AB26" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="AA26" s="3" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB26" s="3" t="n">
+        <v>0.078</v>
+      </c>
       <c r="AC26" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD26" s="3" t="n">
         <v>0.285</v>
@@ -17388,41 +18684,77 @@
       <c r="E27" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
+      <c r="F27" s="3" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>0.556</v>
+      </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>0.278</v>
+      </c>
       <c r="M27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3" t="n"/>
-      <c r="O27" s="3" t="n"/>
-      <c r="P27" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>0.288</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>0.37</v>
+      </c>
       <c r="Q27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="3" t="n"/>
-      <c r="S27" s="3" t="n"/>
-      <c r="T27" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>0.399</v>
+      </c>
       <c r="U27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="3" t="n"/>
-      <c r="W27" s="3" t="n"/>
-      <c r="X27" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X27" s="3" t="n">
+        <v>0.409</v>
+      </c>
       <c r="Y27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="3" t="n"/>
-      <c r="AA27" s="3" t="n"/>
-      <c r="AB27" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="AA27" s="3" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="AB27" s="3" t="n">
+        <v>0.097</v>
+      </c>
       <c r="AC27" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD27" s="3" t="n">
         <v>0.381</v>
@@ -17932,41 +19264,77 @@
       <c r="E31" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
+      <c r="F31" s="3" t="n">
+        <v>0.524</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0.495</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>0.552</v>
+      </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="n"/>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>0.238</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>0.275</v>
+      </c>
       <c r="M31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="3" t="n"/>
-      <c r="O31" s="3" t="n"/>
-      <c r="P31" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>0.343</v>
+      </c>
       <c r="Q31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="3" t="n"/>
-      <c r="S31" s="3" t="n"/>
-      <c r="T31" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>0.397</v>
+      </c>
       <c r="U31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="3" t="n"/>
-      <c r="W31" s="3" t="n"/>
-      <c r="X31" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>0.402</v>
+      </c>
       <c r="Y31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="3" t="n"/>
-      <c r="AA31" s="3" t="n"/>
-      <c r="AB31" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AA31" s="3" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="AB31" s="3" t="n">
+        <v>0.106</v>
+      </c>
       <c r="AC31" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD31" s="3" t="n">
         <v>0.375</v>
@@ -18041,41 +19409,77 @@
       <c r="E32" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F32" s="3" t="n"/>
-      <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3" t="n"/>
+      <c r="F32" s="3" t="n">
+        <v>0.705</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0.673</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0.737</v>
+      </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="n"/>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0.556</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>0.6</v>
+      </c>
       <c r="M32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3" t="n"/>
-      <c r="O32" s="3" t="n"/>
-      <c r="P32" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>0.264</v>
+      </c>
       <c r="Q32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3" t="n"/>
-      <c r="S32" s="3" t="n"/>
-      <c r="T32" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>0.588</v>
+      </c>
       <c r="U32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3" t="n"/>
-      <c r="W32" s="3" t="n"/>
-      <c r="X32" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V32" s="3" t="n">
+        <v>0.5649999999999999</v>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v>0.534</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>0.595</v>
+      </c>
       <c r="Y32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3" t="n"/>
-      <c r="AA32" s="3" t="n"/>
-      <c r="AB32" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="AA32" s="3" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AB32" s="3" t="n">
+        <v>0.09</v>
+      </c>
       <c r="AC32" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD32" s="3" t="n">
         <v>0.188</v>
@@ -18150,41 +19554,77 @@
       <c r="E33" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n"/>
+      <c r="F33" s="3" t="n">
+        <v>0.519</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>0.547</v>
+      </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="n"/>
-      <c r="K33" s="3" t="n"/>
-      <c r="L33" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>0.216</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>0.254</v>
+      </c>
       <c r="M33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3" t="n"/>
-      <c r="O33" s="3" t="n"/>
-      <c r="P33" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>0.34</v>
+      </c>
       <c r="Q33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="3" t="n"/>
-      <c r="S33" s="3" t="n"/>
-      <c r="T33" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>0.387</v>
+      </c>
       <c r="U33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="3" t="n"/>
-      <c r="W33" s="3" t="n"/>
-      <c r="X33" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="W33" s="3" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>0.399</v>
+      </c>
       <c r="Y33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="3" t="n"/>
-      <c r="AA33" s="3" t="n"/>
-      <c r="AB33" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z33" s="3" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="AA33" s="3" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AB33" s="3" t="n">
+        <v>0.09</v>
+      </c>
       <c r="AC33" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD33" s="3" t="n">
         <v>0.368</v>
@@ -19564,41 +21004,77 @@
       <c r="E43" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F43" s="3" t="n"/>
-      <c r="G43" s="3" t="n"/>
-      <c r="H43" s="3" t="n"/>
+      <c r="F43" s="3" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>0.5659999999999999</v>
+      </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="n"/>
-      <c r="K43" s="3" t="n"/>
-      <c r="L43" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>0.263</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>0.301</v>
+      </c>
       <c r="M43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3" t="n"/>
-      <c r="O43" s="3" t="n"/>
-      <c r="P43" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>0.383</v>
+      </c>
       <c r="Q43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="3" t="n"/>
-      <c r="S43" s="3" t="n"/>
-      <c r="T43" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>0.396</v>
+      </c>
       <c r="U43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="3" t="n"/>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>0.405</v>
+      </c>
       <c r="Y43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="3" t="n"/>
-      <c r="AA43" s="3" t="n"/>
-      <c r="AB43" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AA43" s="3" t="n">
+        <v>0.053</v>
+      </c>
+      <c r="AB43" s="3" t="n">
+        <v>0.08799999999999999</v>
+      </c>
       <c r="AC43" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD43" s="3" t="n">
         <v>0.373</v>
@@ -19673,41 +21149,77 @@
       <c r="E44" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F44" s="3" t="n"/>
-      <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="n"/>
+      <c r="F44" s="3" t="n">
+        <v>0.526</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>0.554</v>
+      </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="n"/>
-      <c r="K44" s="3" t="n"/>
-      <c r="L44" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>0.246</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>0.284</v>
+      </c>
       <c r="M44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3" t="n"/>
-      <c r="O44" s="3" t="n"/>
-      <c r="P44" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>0.43</v>
+      </c>
       <c r="Q44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="3" t="n"/>
-      <c r="S44" s="3" t="n"/>
-      <c r="T44" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>0.393</v>
+      </c>
       <c r="U44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" s="3" t="n"/>
-      <c r="W44" s="3" t="n"/>
-      <c r="X44" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>0.409</v>
+      </c>
       <c r="Y44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="3" t="n"/>
-      <c r="AA44" s="3" t="n"/>
-      <c r="AB44" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z44" s="3" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="AA44" s="3" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AB44" s="3" t="n">
+        <v>0.092</v>
+      </c>
       <c r="AC44" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD44" s="3" t="n">
         <v>0.351</v>
@@ -20217,41 +21729,77 @@
       <c r="E48" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F48" s="3" t="n"/>
-      <c r="G48" s="3" t="n"/>
-      <c r="H48" s="3" t="n"/>
+      <c r="F48" s="3" t="n">
+        <v>0.527</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0.499</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>0.555</v>
+      </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="n"/>
-      <c r="K48" s="3" t="n"/>
-      <c r="L48" s="3" t="n"/>
+        <v>498</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>0.235</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>0.199</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>0.271</v>
+      </c>
       <c r="M48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="3" t="n"/>
-      <c r="O48" s="3" t="n"/>
-      <c r="P48" s="3" t="n"/>
+        <v>498</v>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>0.353</v>
+      </c>
+      <c r="O48" s="3" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="P48" s="3" t="n">
+        <v>0.396</v>
+      </c>
       <c r="Q48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="3" t="n"/>
-      <c r="S48" s="3" t="n"/>
-      <c r="T48" s="3" t="n"/>
+        <v>498</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="S48" s="3" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="T48" s="3" t="n">
+        <v>0.373</v>
+      </c>
       <c r="U48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="3" t="n"/>
-      <c r="W48" s="3" t="n"/>
-      <c r="X48" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V48" s="3" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="W48" s="3" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="X48" s="3" t="n">
+        <v>0.394</v>
+      </c>
       <c r="Y48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" s="3" t="n"/>
-      <c r="AA48" s="3" t="n"/>
-      <c r="AB48" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z48" s="3" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="AA48" s="3" t="n">
+        <v>0.066</v>
+      </c>
+      <c r="AB48" s="3" t="n">
+        <v>0.103</v>
+      </c>
       <c r="AC48" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD48" s="3" t="n">
         <v>0.369</v>
@@ -20326,41 +21874,77 @@
       <c r="E49" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F49" s="3" t="n"/>
-      <c r="G49" s="3" t="n"/>
-      <c r="H49" s="3" t="n"/>
+      <c r="F49" s="3" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0.553</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>0.619</v>
+      </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3" t="n"/>
-      <c r="K49" s="3" t="n"/>
-      <c r="L49" s="3" t="n"/>
+        <v>498</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>0.428</v>
+      </c>
       <c r="M49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="3" t="n"/>
-      <c r="O49" s="3" t="n"/>
-      <c r="P49" s="3" t="n"/>
+        <v>498</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>0.42</v>
+      </c>
       <c r="Q49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" s="3" t="n"/>
-      <c r="S49" s="3" t="n"/>
-      <c r="T49" s="3" t="n"/>
+        <v>498</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="S49" s="3" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="T49" s="3" t="n">
+        <v>0.5669999999999999</v>
+      </c>
       <c r="U49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" s="3" t="n"/>
-      <c r="W49" s="3" t="n"/>
-      <c r="X49" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V49" s="3" t="n">
+        <v>0.518</v>
+      </c>
+      <c r="W49" s="3" t="n">
+        <v>0.487</v>
+      </c>
+      <c r="X49" s="3" t="n">
+        <v>0.547</v>
+      </c>
       <c r="Y49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" s="3" t="n"/>
-      <c r="AA49" s="3" t="n"/>
-      <c r="AB49" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z49" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AA49" s="3" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="AB49" s="3" t="n">
+        <v>0.108</v>
+      </c>
       <c r="AC49" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD49" s="3" t="n">
         <v>0.193</v>
@@ -20435,41 +22019,77 @@
       <c r="E50" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F50" s="3" t="n"/>
-      <c r="G50" s="3" t="n"/>
-      <c r="H50" s="3" t="n"/>
+      <c r="F50" s="3" t="n">
+        <v>0.517</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>0.545</v>
+      </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="3" t="n"/>
-      <c r="K50" s="3" t="n"/>
-      <c r="L50" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>0.218</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>0.184</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>0.256</v>
+      </c>
       <c r="M50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="3" t="n"/>
-      <c r="O50" s="3" t="n"/>
-      <c r="P50" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="O50" s="3" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="P50" s="3" t="n">
+        <v>0.392</v>
+      </c>
       <c r="Q50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="3" t="n"/>
-      <c r="S50" s="3" t="n"/>
-      <c r="T50" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="S50" s="3" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="T50" s="3" t="n">
+        <v>0.39</v>
+      </c>
       <c r="U50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" s="3" t="n"/>
-      <c r="W50" s="3" t="n"/>
-      <c r="X50" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V50" s="3" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="W50" s="3" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="X50" s="3" t="n">
+        <v>0.395</v>
+      </c>
       <c r="Y50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" s="3" t="n"/>
-      <c r="AA50" s="3" t="n"/>
-      <c r="AB50" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z50" s="3" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="AA50" s="3" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="AB50" s="3" t="n">
+        <v>0.096</v>
+      </c>
       <c r="AC50" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD50" s="3" t="n">
         <v>0.348</v>
@@ -21992,41 +23612,77 @@
       <c r="E10" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F10" s="3" t="n"/>
-      <c r="G10" s="3" t="n"/>
-      <c r="H10" s="3" t="n"/>
+      <c r="F10" s="3" t="n">
+        <v>0.482</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0.513</v>
+      </c>
       <c r="I10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" s="3" t="n"/>
-      <c r="K10" s="3" t="n"/>
-      <c r="L10" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0.266</v>
+      </c>
       <c r="M10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="3" t="n"/>
-      <c r="O10" s="3" t="n"/>
-      <c r="P10" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N10" s="3" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="O10" s="3" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="P10" s="3" t="n">
+        <v>0.408</v>
+      </c>
       <c r="Q10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" s="3" t="n"/>
-      <c r="S10" s="3" t="n"/>
-      <c r="T10" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>0.354</v>
+      </c>
       <c r="U10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="n"/>
-      <c r="W10" s="3" t="n"/>
-      <c r="X10" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>0.353</v>
+      </c>
       <c r="Y10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="3" t="n"/>
-      <c r="AA10" s="3" t="n"/>
-      <c r="AB10" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="AA10" s="3" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="AB10" s="3" t="n">
+        <v>0.112</v>
+      </c>
       <c r="AC10" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD10" s="3" t="n">
         <v>0.356</v>
@@ -22536,41 +24192,77 @@
       <c r="E14" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F14" s="3" t="n"/>
-      <c r="G14" s="3" t="n"/>
-      <c r="H14" s="3" t="n"/>
+      <c r="F14" s="3" t="n">
+        <v>0.489</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0.458</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0.52</v>
+      </c>
       <c r="I14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3" t="n"/>
-      <c r="K14" s="3" t="n"/>
-      <c r="L14" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0.182</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0.259</v>
+      </c>
       <c r="M14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="3" t="n"/>
-      <c r="O14" s="3" t="n"/>
-      <c r="P14" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="N14" s="3" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="O14" s="3" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="P14" s="3" t="n">
+        <v>0.405</v>
+      </c>
       <c r="Q14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R14" s="3" t="n"/>
-      <c r="S14" s="3" t="n"/>
-      <c r="T14" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="S14" s="3" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="T14" s="3" t="n">
+        <v>0.366</v>
+      </c>
       <c r="U14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3" t="n"/>
-      <c r="W14" s="3" t="n"/>
-      <c r="X14" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V14" s="3" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="X14" s="3" t="n">
+        <v>0.37</v>
+      </c>
       <c r="Y14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="n"/>
-      <c r="AA14" s="3" t="n"/>
-      <c r="AB14" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z14" s="3" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AA14" s="3" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="AB14" s="3" t="n">
+        <v>0.128</v>
+      </c>
       <c r="AC14" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD14" s="3" t="n">
         <v>0.351</v>
@@ -22645,41 +24337,77 @@
       <c r="E15" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F15" s="3" t="n"/>
-      <c r="G15" s="3" t="n"/>
-      <c r="H15" s="3" t="n"/>
+      <c r="F15" s="3" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>0.587</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0.654</v>
+      </c>
       <c r="I15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" s="3" t="n"/>
-      <c r="K15" s="3" t="n"/>
-      <c r="L15" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>0.496</v>
+      </c>
       <c r="M15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="3" t="n"/>
-      <c r="O15" s="3" t="n"/>
-      <c r="P15" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N15" s="3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="O15" s="3" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="P15" s="3" t="n">
+        <v>0.454</v>
+      </c>
       <c r="Q15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3" t="n"/>
-      <c r="S15" s="3" t="n"/>
-      <c r="T15" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>0.505</v>
+      </c>
+      <c r="S15" s="3" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="T15" s="3" t="n">
+        <v>0.536</v>
+      </c>
       <c r="U15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" s="3" t="n"/>
-      <c r="W15" s="3" t="n"/>
-      <c r="X15" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V15" s="3" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="W15" s="3" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="X15" s="3" t="n">
+        <v>0.511</v>
+      </c>
       <c r="Y15" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="3" t="n"/>
-      <c r="AA15" s="3" t="n"/>
-      <c r="AB15" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z15" s="3" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="AA15" s="3" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="AB15" s="3" t="n">
+        <v>0.117</v>
+      </c>
       <c r="AC15" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD15" s="3" t="n">
         <v>0.261</v>
@@ -22754,41 +24482,77 @@
       <c r="E16" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F16" s="3" t="n"/>
-      <c r="G16" s="3" t="n"/>
-      <c r="H16" s="3" t="n"/>
+      <c r="F16" s="3" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0.504</v>
+      </c>
       <c r="I16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J16" s="3" t="n"/>
-      <c r="K16" s="3" t="n"/>
-      <c r="L16" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0.176</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>0.248</v>
+      </c>
       <c r="M16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="3" t="n"/>
-      <c r="O16" s="3" t="n"/>
-      <c r="P16" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N16" s="3" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="O16" s="3" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="P16" s="3" t="n">
+        <v>0.414</v>
+      </c>
       <c r="Q16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" s="3" t="n"/>
-      <c r="S16" s="3" t="n"/>
-      <c r="T16" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="S16" s="3" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="T16" s="3" t="n">
+        <v>0.337</v>
+      </c>
       <c r="U16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" s="3" t="n"/>
-      <c r="W16" s="3" t="n"/>
-      <c r="X16" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V16" s="3" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="W16" s="3" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="X16" s="3" t="n">
+        <v>0.343</v>
+      </c>
       <c r="Y16" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z16" s="3" t="n"/>
-      <c r="AA16" s="3" t="n"/>
-      <c r="AB16" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z16" s="3" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="AA16" s="3" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AB16" s="3" t="n">
+        <v>0.127</v>
+      </c>
       <c r="AC16" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD16" s="3" t="n">
         <v>0.345</v>
@@ -24023,41 +25787,77 @@
       <c r="E25" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F25" s="3" t="n"/>
-      <c r="G25" s="3" t="n"/>
-      <c r="H25" s="3" t="n"/>
+      <c r="F25" s="3" t="n">
+        <v>0.6870000000000001</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>0.654</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>0.719</v>
+      </c>
       <c r="I25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="3" t="n"/>
-      <c r="K25" s="3" t="n"/>
-      <c r="L25" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>0.538</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>0.494</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>0.58</v>
+      </c>
       <c r="M25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="3" t="n"/>
-      <c r="O25" s="3" t="n"/>
-      <c r="P25" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N25" s="3" t="n">
+        <v>0.224</v>
+      </c>
+      <c r="O25" s="3" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="P25" s="3" t="n">
+        <v>0.26</v>
+      </c>
       <c r="Q25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R25" s="3" t="n"/>
-      <c r="S25" s="3" t="n"/>
-      <c r="T25" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>0.545</v>
+      </c>
+      <c r="S25" s="3" t="n">
+        <v>0.514</v>
+      </c>
+      <c r="T25" s="3" t="n">
+        <v>0.578</v>
+      </c>
       <c r="U25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" s="3" t="n"/>
-      <c r="W25" s="3" t="n"/>
-      <c r="X25" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V25" s="3" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="W25" s="3" t="n">
+        <v>0.492</v>
+      </c>
+      <c r="X25" s="3" t="n">
+        <v>0.5580000000000001</v>
+      </c>
       <c r="Y25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z25" s="3" t="n"/>
-      <c r="AA25" s="3" t="n"/>
-      <c r="AB25" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v>0.052</v>
+      </c>
+      <c r="AA25" s="3" t="n">
+        <v>0.038</v>
+      </c>
+      <c r="AB25" s="3" t="n">
+        <v>0.068</v>
+      </c>
       <c r="AC25" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD25" s="3" t="n">
         <v>0.179</v>
@@ -24132,41 +25932,77 @@
       <c r="E26" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F26" s="3" t="n"/>
-      <c r="G26" s="3" t="n"/>
-      <c r="H26" s="3" t="n"/>
+      <c r="F26" s="3" t="n">
+        <v>0.5669999999999999</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0.537</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>0.598</v>
+      </c>
       <c r="I26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="n"/>
-      <c r="K26" s="3" t="n"/>
-      <c r="L26" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>0.278</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>0.358</v>
+      </c>
       <c r="M26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="3" t="n"/>
-      <c r="O26" s="3" t="n"/>
-      <c r="P26" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N26" s="3" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="O26" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P26" s="3" t="n">
+        <v>0.352</v>
+      </c>
       <c r="Q26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" s="3" t="n"/>
-      <c r="S26" s="3" t="n"/>
-      <c r="T26" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>0.376</v>
+      </c>
       <c r="U26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="3" t="n"/>
-      <c r="W26" s="3" t="n"/>
-      <c r="X26" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>0.386</v>
+      </c>
       <c r="Y26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="3" t="n"/>
-      <c r="AA26" s="3" t="n"/>
-      <c r="AB26" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="AA26" s="3" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="AB26" s="3" t="n">
+        <v>0.08799999999999999</v>
+      </c>
       <c r="AC26" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD26" s="3" t="n">
         <v>0.275</v>
@@ -24241,41 +26077,77 @@
       <c r="E27" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n"/>
-      <c r="H27" s="3" t="n"/>
+      <c r="F27" s="3" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0.467</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>0.527</v>
+      </c>
       <c r="I27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="n"/>
-      <c r="K27" s="3" t="n"/>
-      <c r="L27" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0.228</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>0.266</v>
+      </c>
       <c r="M27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="3" t="n"/>
-      <c r="O27" s="3" t="n"/>
-      <c r="P27" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N27" s="3" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="O27" s="3" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="P27" s="3" t="n">
+        <v>0.378</v>
+      </c>
       <c r="Q27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R27" s="3" t="n"/>
-      <c r="S27" s="3" t="n"/>
-      <c r="T27" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="S27" s="3" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="T27" s="3" t="n">
+        <v>0.354</v>
+      </c>
       <c r="U27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" s="3" t="n"/>
-      <c r="W27" s="3" t="n"/>
-      <c r="X27" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V27" s="3" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="W27" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X27" s="3" t="n">
+        <v>0.357</v>
+      </c>
       <c r="Y27" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" s="3" t="n"/>
-      <c r="AA27" s="3" t="n"/>
-      <c r="AB27" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="AA27" s="3" t="n">
+        <v>0.058</v>
+      </c>
+      <c r="AB27" s="3" t="n">
+        <v>0.096</v>
+      </c>
       <c r="AC27" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD27" s="3" t="n">
         <v>0.361</v>
@@ -24785,41 +26657,77 @@
       <c r="E31" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F31" s="3" t="n"/>
-      <c r="G31" s="3" t="n"/>
-      <c r="H31" s="3" t="n"/>
+      <c r="F31" s="3" t="n">
+        <v>0.512</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>0.543</v>
+      </c>
       <c r="I31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J31" s="3" t="n"/>
-      <c r="K31" s="3" t="n"/>
-      <c r="L31" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>0.276</v>
+      </c>
       <c r="M31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="3" t="n"/>
-      <c r="O31" s="3" t="n"/>
-      <c r="P31" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N31" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="O31" s="3" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="P31" s="3" t="n">
+        <v>0.348</v>
+      </c>
       <c r="Q31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R31" s="3" t="n"/>
-      <c r="S31" s="3" t="n"/>
-      <c r="T31" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="S31" s="3" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="T31" s="3" t="n">
+        <v>0.362</v>
+      </c>
       <c r="U31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" s="3" t="n"/>
-      <c r="W31" s="3" t="n"/>
-      <c r="X31" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V31" s="3" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="W31" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="X31" s="3" t="n">
+        <v>0.358</v>
+      </c>
       <c r="Y31" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="3" t="n"/>
-      <c r="AA31" s="3" t="n"/>
-      <c r="AB31" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z31" s="3" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AA31" s="3" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="AB31" s="3" t="n">
+        <v>0.108</v>
+      </c>
       <c r="AC31" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD31" s="3" t="n">
         <v>0.357</v>
@@ -24894,41 +26802,77 @@
       <c r="E32" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F32" s="3" t="n"/>
-      <c r="G32" s="3" t="n"/>
-      <c r="H32" s="3" t="n"/>
+      <c r="F32" s="3" t="n">
+        <v>0.675</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0.642</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0.709</v>
+      </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="n"/>
-      <c r="K32" s="3" t="n"/>
-      <c r="L32" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0.523</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0.479</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>0.571</v>
+      </c>
       <c r="M32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="3" t="n"/>
-      <c r="O32" s="3" t="n"/>
-      <c r="P32" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="O32" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P32" s="3" t="n">
+        <v>0.275</v>
+      </c>
       <c r="Q32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R32" s="3" t="n"/>
-      <c r="S32" s="3" t="n"/>
-      <c r="T32" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>0.508</v>
+      </c>
+      <c r="S32" s="3" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="T32" s="3" t="n">
+        <v>0.541</v>
+      </c>
       <c r="U32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V32" s="3" t="n"/>
-      <c r="W32" s="3" t="n"/>
-      <c r="X32" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V32" s="3" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="W32" s="3" t="n">
+        <v>0.475</v>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v>0.539</v>
+      </c>
       <c r="Y32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z32" s="3" t="n"/>
-      <c r="AA32" s="3" t="n"/>
-      <c r="AB32" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z32" s="3" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="AA32" s="3" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AB32" s="3" t="n">
+        <v>0.078</v>
+      </c>
       <c r="AC32" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD32" s="3" t="n">
         <v>0.188</v>
@@ -25003,41 +26947,77 @@
       <c r="E33" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F33" s="3" t="n"/>
-      <c r="G33" s="3" t="n"/>
-      <c r="H33" s="3" t="n"/>
+      <c r="F33" s="3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>0.51</v>
+      </c>
       <c r="I33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="3" t="n"/>
-      <c r="K33" s="3" t="n"/>
-      <c r="L33" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>0.192</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>0.158</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>0.228</v>
+      </c>
       <c r="M33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="3" t="n"/>
-      <c r="O33" s="3" t="n"/>
-      <c r="P33" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O33" s="3" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="P33" s="3" t="n">
+        <v>0.392</v>
+      </c>
       <c r="Q33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R33" s="3" t="n"/>
-      <c r="S33" s="3" t="n"/>
-      <c r="T33" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="S33" s="3" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="T33" s="3" t="n">
+        <v>0.344</v>
+      </c>
       <c r="U33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V33" s="3" t="n"/>
-      <c r="W33" s="3" t="n"/>
-      <c r="X33" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V33" s="3" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="W33" s="3" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v>0.361</v>
+      </c>
       <c r="Y33" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="3" t="n"/>
-      <c r="AA33" s="3" t="n"/>
-      <c r="AB33" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z33" s="3" t="n">
+        <v>0.08500000000000001</v>
+      </c>
+      <c r="AA33" s="3" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="AB33" s="3" t="n">
+        <v>0.105</v>
+      </c>
       <c r="AC33" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD33" s="3" t="n">
         <v>0.345</v>
@@ -26417,41 +28397,77 @@
       <c r="E43" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F43" s="3" t="n"/>
-      <c r="G43" s="3" t="n"/>
-      <c r="H43" s="3" t="n"/>
+      <c r="F43" s="3" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0.444</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>0.5</v>
+      </c>
       <c r="I43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="3" t="n"/>
-      <c r="K43" s="3" t="n"/>
-      <c r="L43" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>0.186</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>0.154</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>0.222</v>
+      </c>
       <c r="M43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="3" t="n"/>
-      <c r="O43" s="3" t="n"/>
-      <c r="P43" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N43" s="3" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="O43" s="3" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="P43" s="3" t="n">
+        <v>0.43</v>
+      </c>
       <c r="Q43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R43" s="3" t="n"/>
-      <c r="S43" s="3" t="n"/>
-      <c r="T43" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="S43" s="3" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="T43" s="3" t="n">
+        <v>0.344</v>
+      </c>
       <c r="U43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V43" s="3" t="n"/>
-      <c r="W43" s="3" t="n"/>
-      <c r="X43" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V43" s="3" t="n">
+        <v>0.334</v>
+      </c>
+      <c r="W43" s="3" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="X43" s="3" t="n">
+        <v>0.363</v>
+      </c>
       <c r="Y43" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z43" s="3" t="n"/>
-      <c r="AA43" s="3" t="n"/>
-      <c r="AB43" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z43" s="3" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="AA43" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AB43" s="3" t="n">
+        <v>0.107</v>
+      </c>
       <c r="AC43" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD43" s="3" t="n">
         <v>0.349</v>
@@ -26526,41 +28542,77 @@
       <c r="E44" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F44" s="3" t="n"/>
-      <c r="G44" s="3" t="n"/>
-      <c r="H44" s="3" t="n"/>
+      <c r="F44" s="3" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0.439</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>0.501</v>
+      </c>
       <c r="I44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3" t="n"/>
-      <c r="K44" s="3" t="n"/>
-      <c r="L44" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>0.24</v>
+      </c>
       <c r="M44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="3" t="n"/>
-      <c r="O44" s="3" t="n"/>
-      <c r="P44" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="N44" s="3" t="n">
+        <v>0.411</v>
+      </c>
+      <c r="O44" s="3" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="P44" s="3" t="n">
+        <v>0.455</v>
+      </c>
       <c r="Q44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R44" s="3" t="n"/>
-      <c r="S44" s="3" t="n"/>
-      <c r="T44" s="3" t="n"/>
+        <v>499</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="S44" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="T44" s="3" t="n">
+        <v>0.337</v>
+      </c>
       <c r="U44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V44" s="3" t="n"/>
-      <c r="W44" s="3" t="n"/>
-      <c r="X44" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V44" s="3" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="W44" s="3" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="X44" s="3" t="n">
+        <v>0.34</v>
+      </c>
       <c r="Y44" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z44" s="3" t="n"/>
-      <c r="AA44" s="3" t="n"/>
-      <c r="AB44" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z44" s="3" t="n">
+        <v>0.082</v>
+      </c>
+      <c r="AA44" s="3" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="AB44" s="3" t="n">
+        <v>0.103</v>
+      </c>
       <c r="AC44" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD44" s="3" t="n">
         <v>0.314</v>
@@ -27070,41 +29122,77 @@
       <c r="E48" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F48" s="3" t="n"/>
-      <c r="G48" s="3" t="n"/>
-      <c r="H48" s="3" t="n"/>
+      <c r="F48" s="3" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>0.503</v>
+      </c>
       <c r="I48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="3" t="n"/>
-      <c r="K48" s="3" t="n"/>
-      <c r="L48" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>0.204</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>0.242</v>
+      </c>
       <c r="M48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="3" t="n"/>
-      <c r="O48" s="3" t="n"/>
-      <c r="P48" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N48" s="3" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="O48" s="3" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="P48" s="3" t="n">
+        <v>0.442</v>
+      </c>
       <c r="Q48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R48" s="3" t="n"/>
-      <c r="S48" s="3" t="n"/>
-      <c r="T48" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="S48" s="3" t="n">
+        <v>0.307</v>
+      </c>
+      <c r="T48" s="3" t="n">
+        <v>0.364</v>
+      </c>
       <c r="U48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V48" s="3" t="n"/>
-      <c r="W48" s="3" t="n"/>
-      <c r="X48" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V48" s="3" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W48" s="3" t="n">
+        <v>0.312</v>
+      </c>
+      <c r="X48" s="3" t="n">
+        <v>0.372</v>
+      </c>
       <c r="Y48" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z48" s="3" t="n"/>
-      <c r="AA48" s="3" t="n"/>
-      <c r="AB48" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z48" s="3" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="AA48" s="3" t="n">
+        <v>0.081</v>
+      </c>
+      <c r="AB48" s="3" t="n">
+        <v>0.123</v>
+      </c>
       <c r="AC48" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD48" s="3" t="n">
         <v>0.343</v>
@@ -27179,41 +29267,77 @@
       <c r="E49" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F49" s="3" t="n"/>
-      <c r="G49" s="3" t="n"/>
-      <c r="H49" s="3" t="n"/>
+      <c r="F49" s="3" t="n">
+        <v>0.541</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0.507</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>0.573</v>
+      </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J49" s="3" t="n"/>
-      <c r="K49" s="3" t="n"/>
-      <c r="L49" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>0.394</v>
+      </c>
       <c r="M49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="3" t="n"/>
-      <c r="O49" s="3" t="n"/>
-      <c r="P49" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N49" s="3" t="n">
+        <v>0.442</v>
+      </c>
+      <c r="O49" s="3" t="n">
+        <v>0.398</v>
+      </c>
+      <c r="P49" s="3" t="n">
+        <v>0.484</v>
+      </c>
       <c r="Q49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R49" s="3" t="n"/>
-      <c r="S49" s="3" t="n"/>
-      <c r="T49" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>0.483</v>
+      </c>
+      <c r="S49" s="3" t="n">
+        <v>0.452</v>
+      </c>
+      <c r="T49" s="3" t="n">
+        <v>0.516</v>
+      </c>
       <c r="U49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" s="3" t="n"/>
-      <c r="W49" s="3" t="n"/>
-      <c r="X49" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V49" s="3" t="n">
+        <v>0.451</v>
+      </c>
+      <c r="W49" s="3" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="X49" s="3" t="n">
+        <v>0.483</v>
+      </c>
       <c r="Y49" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" s="3" t="n"/>
-      <c r="AA49" s="3" t="n"/>
-      <c r="AB49" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z49" s="3" t="n">
+        <v>0.08699999999999999</v>
+      </c>
+      <c r="AA49" s="3" t="n">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="AB49" s="3" t="n">
+        <v>0.106</v>
+      </c>
       <c r="AC49" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD49" s="3" t="n">
         <v>0.187</v>
@@ -27288,41 +29412,77 @@
       <c r="E50" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="F50" s="3" t="n"/>
-      <c r="G50" s="3" t="n"/>
-      <c r="H50" s="3" t="n"/>
+      <c r="F50" s="3" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0.427</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>0.483</v>
+      </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="3" t="n"/>
-      <c r="K50" s="3" t="n"/>
-      <c r="L50" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>0.168</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>0.138</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>0.202</v>
+      </c>
       <c r="M50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="3" t="n"/>
-      <c r="O50" s="3" t="n"/>
-      <c r="P50" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="N50" s="3" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="O50" s="3" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="P50" s="3" t="n">
+        <v>0.454</v>
+      </c>
       <c r="Q50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="R50" s="3" t="n"/>
-      <c r="S50" s="3" t="n"/>
-      <c r="T50" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="S50" s="3" t="n">
+        <v>0.264</v>
+      </c>
+      <c r="T50" s="3" t="n">
+        <v>0.321</v>
+      </c>
       <c r="U50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V50" s="3" t="n"/>
-      <c r="W50" s="3" t="n"/>
-      <c r="X50" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V50" s="3" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="W50" s="3" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="X50" s="3" t="n">
+        <v>0.318</v>
+      </c>
       <c r="Y50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z50" s="3" t="n"/>
-      <c r="AA50" s="3" t="n"/>
-      <c r="AB50" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z50" s="3" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="AA50" s="3" t="n">
+        <v>0.074</v>
+      </c>
+      <c r="AB50" s="3" t="n">
+        <v>0.113</v>
+      </c>
       <c r="AC50" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD50" s="3" t="n">
         <v>0.322</v>

--- a/research_materials/03_results/main_results.xlsx
+++ b/research_materials/03_results/main_results.xlsx
@@ -462,7 +462,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Built: 2026-10-07 02:47 by src/build_research_materials.py</t>
+          <t>Built: 2026-10-07 02:57 by src/build_research_materials.py</t>
         </is>
       </c>
     </row>
@@ -1819,23 +1819,41 @@
       <c r="Q9" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="R9" s="3" t="n"/>
-      <c r="S9" s="3" t="n"/>
-      <c r="T9" s="3" t="n"/>
+      <c r="R9" s="3" t="n">
+        <v>0.525</v>
+      </c>
+      <c r="S9" s="3" t="n">
+        <v>0.493</v>
+      </c>
+      <c r="T9" s="3" t="n">
+        <v>0.5590000000000001</v>
+      </c>
       <c r="U9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" s="3" t="n"/>
-      <c r="W9" s="3" t="n"/>
-      <c r="X9" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V9" s="3" t="n">
+        <v>0.528</v>
+      </c>
+      <c r="W9" s="3" t="n">
+        <v>0.496</v>
+      </c>
+      <c r="X9" s="3" t="n">
+        <v>0.5629999999999999</v>
+      </c>
       <c r="Y9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="3" t="n"/>
-      <c r="AA9" s="3" t="n"/>
-      <c r="AB9" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z9" s="3" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="AA9" s="3" t="n">
+        <v>0.033</v>
+      </c>
+      <c r="AB9" s="3" t="n">
+        <v>0.06</v>
+      </c>
       <c r="AC9" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD9" s="3" t="n">
         <v>0.579</v>
@@ -3946,23 +3964,41 @@
       <c r="Q24" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="R24" s="3" t="n"/>
-      <c r="S24" s="3" t="n"/>
-      <c r="T24" s="3" t="n"/>
+      <c r="R24" s="3" t="n">
+        <v>0.388</v>
+      </c>
+      <c r="S24" s="3" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="T24" s="3" t="n">
+        <v>0.421</v>
+      </c>
       <c r="U24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" s="3" t="n"/>
-      <c r="W24" s="3" t="n"/>
-      <c r="X24" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V24" s="3" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="W24" s="3" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="X24" s="3" t="n">
+        <v>0.413</v>
+      </c>
       <c r="Y24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z24" s="3" t="n"/>
-      <c r="AA24" s="3" t="n"/>
-      <c r="AB24" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z24" s="3" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="AA24" s="3" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="AB24" s="3" t="n">
+        <v>0.089</v>
+      </c>
       <c r="AC24" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD24" s="3" t="n">
         <v>0.414</v>
@@ -6508,23 +6544,41 @@
       <c r="Q42" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="R42" s="3" t="n"/>
-      <c r="S42" s="3" t="n"/>
-      <c r="T42" s="3" t="n"/>
+      <c r="R42" s="3" t="n">
+        <v>0.697</v>
+      </c>
+      <c r="S42" s="3" t="n">
+        <v>0.665</v>
+      </c>
+      <c r="T42" s="3" t="n">
+        <v>0.731</v>
+      </c>
       <c r="U42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V42" s="3" t="n"/>
-      <c r="W42" s="3" t="n"/>
-      <c r="X42" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V42" s="3" t="n">
+        <v>0.701</v>
+      </c>
+      <c r="W42" s="3" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="X42" s="3" t="n">
+        <v>0.734</v>
+      </c>
       <c r="Y42" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z42" s="3" t="n"/>
-      <c r="AA42" s="3" t="n"/>
-      <c r="AB42" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="AA42" s="3" t="n">
+        <v>0.018</v>
+      </c>
+      <c r="AB42" s="3" t="n">
+        <v>0.038</v>
+      </c>
       <c r="AC42" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD42" s="3" t="n">
         <v>0.796</v>
@@ -9243,23 +9297,41 @@
       <c r="Q10" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="R10" s="3" t="n"/>
-      <c r="S10" s="3" t="n"/>
-      <c r="T10" s="3" t="n"/>
+      <c r="R10" s="3" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>0.417</v>
+      </c>
       <c r="U10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="n"/>
-      <c r="W10" s="3" t="n"/>
-      <c r="X10" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>0.342</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>0.426</v>
+      </c>
       <c r="Y10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="3" t="n"/>
-      <c r="AA10" s="3" t="n"/>
-      <c r="AB10" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="AA10" s="3" t="n">
+        <v>0.047</v>
+      </c>
+      <c r="AB10" s="3" t="n">
+        <v>0.092</v>
+      </c>
       <c r="AC10" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="AD10" s="3" t="n">
         <v>0.361</v>
@@ -11545,23 +11617,41 @@
       <c r="Q26" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="R26" s="3" t="n"/>
-      <c r="S26" s="3" t="n"/>
-      <c r="T26" s="3" t="n"/>
+      <c r="R26" s="3" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>0.368</v>
+      </c>
       <c r="U26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="3" t="n"/>
-      <c r="W26" s="3" t="n"/>
-      <c r="X26" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>0.372</v>
+      </c>
       <c r="Y26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="3" t="n"/>
-      <c r="AA26" s="3" t="n"/>
-      <c r="AB26" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AA26" s="3" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB26" s="3" t="n">
+        <v>0.117</v>
+      </c>
       <c r="AC26" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="AD26" s="3" t="n">
         <v>0.308</v>
@@ -14282,23 +14372,41 @@
       <c r="Q45" s="2" t="n">
         <v>279</v>
       </c>
-      <c r="R45" s="3" t="n"/>
-      <c r="S45" s="3" t="n"/>
-      <c r="T45" s="3" t="n"/>
+      <c r="R45" s="3" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>0.491</v>
+      </c>
       <c r="U45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" s="3" t="n"/>
-      <c r="W45" s="3" t="n"/>
-      <c r="X45" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>0.521</v>
+      </c>
       <c r="Y45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" s="3" t="n"/>
-      <c r="AA45" s="3" t="n"/>
-      <c r="AB45" s="3" t="n"/>
+        <v>279</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="AA45" s="3" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="AB45" s="3" t="n">
+        <v>0.094</v>
+      </c>
       <c r="AC45" s="2" t="n">
-        <v>0</v>
+        <v>279</v>
       </c>
       <c r="AD45" s="3" t="n">
         <v>0.451</v>
@@ -17017,23 +17125,41 @@
       <c r="Q10" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="R10" s="3" t="n"/>
-      <c r="S10" s="3" t="n"/>
-      <c r="T10" s="3" t="n"/>
+      <c r="R10" s="3" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>0.378</v>
+      </c>
       <c r="U10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="n"/>
-      <c r="W10" s="3" t="n"/>
-      <c r="X10" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>0.387</v>
+      </c>
       <c r="Y10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="3" t="n"/>
-      <c r="AA10" s="3" t="n"/>
-      <c r="AB10" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="AA10" s="3" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="AB10" s="3" t="n">
+        <v>0.098</v>
+      </c>
       <c r="AC10" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD10" s="3" t="n">
         <v>0.332</v>
@@ -19319,23 +19445,41 @@
       <c r="Q26" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="R26" s="3" t="n"/>
-      <c r="S26" s="3" t="n"/>
-      <c r="T26" s="3" t="n"/>
+      <c r="R26" s="3" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>0.342</v>
+      </c>
       <c r="U26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="3" t="n"/>
-      <c r="W26" s="3" t="n"/>
-      <c r="X26" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>0.362</v>
+      </c>
       <c r="Y26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="3" t="n"/>
-      <c r="AA26" s="3" t="n"/>
-      <c r="AB26" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>0.08599999999999999</v>
+      </c>
+      <c r="AA26" s="3" t="n">
+        <v>0.067</v>
+      </c>
+      <c r="AB26" s="3" t="n">
+        <v>0.105</v>
+      </c>
       <c r="AC26" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD26" s="3" t="n">
         <v>0.306</v>
@@ -22056,23 +22200,41 @@
       <c r="Q45" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="R45" s="3" t="n"/>
-      <c r="S45" s="3" t="n"/>
-      <c r="T45" s="3" t="n"/>
+      <c r="R45" s="3" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>0.377</v>
+      </c>
       <c r="U45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" s="3" t="n"/>
-      <c r="W45" s="3" t="n"/>
-      <c r="X45" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>0.383</v>
+      </c>
       <c r="Y45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" s="3" t="n"/>
-      <c r="AA45" s="3" t="n"/>
-      <c r="AB45" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>0.076</v>
+      </c>
+      <c r="AA45" s="3" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="AB45" s="3" t="n">
+        <v>0.093</v>
+      </c>
       <c r="AC45" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD45" s="3" t="n">
         <v>0.331</v>
@@ -24791,23 +24953,41 @@
       <c r="Q10" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="R10" s="3" t="n"/>
-      <c r="S10" s="3" t="n"/>
-      <c r="T10" s="3" t="n"/>
+      <c r="R10" s="3" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="S10" s="3" t="n">
+        <v>0.276</v>
+      </c>
+      <c r="T10" s="3" t="n">
+        <v>0.335</v>
+      </c>
       <c r="U10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V10" s="3" t="n"/>
-      <c r="W10" s="3" t="n"/>
-      <c r="X10" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V10" s="3" t="n">
+        <v>0.304</v>
+      </c>
+      <c r="W10" s="3" t="n">
+        <v>0.274</v>
+      </c>
+      <c r="X10" s="3" t="n">
+        <v>0.333</v>
+      </c>
       <c r="Y10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="3" t="n"/>
-      <c r="AA10" s="3" t="n"/>
-      <c r="AB10" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z10" s="3" t="n">
+        <v>0.103</v>
+      </c>
+      <c r="AA10" s="3" t="n">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="AB10" s="3" t="n">
+        <v>0.124</v>
+      </c>
       <c r="AC10" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD10" s="3" t="n">
         <v>0.31</v>
@@ -27093,23 +27273,41 @@
       <c r="Q26" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="R26" s="3" t="n"/>
-      <c r="S26" s="3" t="n"/>
-      <c r="T26" s="3" t="n"/>
+      <c r="R26" s="3" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="S26" s="3" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="T26" s="3" t="n">
+        <v>0.323</v>
+      </c>
       <c r="U26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" s="3" t="n"/>
-      <c r="W26" s="3" t="n"/>
-      <c r="X26" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V26" s="3" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="W26" s="3" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="X26" s="3" t="n">
+        <v>0.313</v>
+      </c>
       <c r="Y26" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" s="3" t="n"/>
-      <c r="AA26" s="3" t="n"/>
-      <c r="AB26" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="AA26" s="3" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="AB26" s="3" t="n">
+        <v>0.101</v>
+      </c>
       <c r="AC26" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD26" s="3" t="n">
         <v>0.289</v>
@@ -29830,23 +30028,41 @@
       <c r="Q45" s="2" t="n">
         <v>500</v>
       </c>
-      <c r="R45" s="3" t="n"/>
-      <c r="S45" s="3" t="n"/>
-      <c r="T45" s="3" t="n"/>
+      <c r="R45" s="3" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v>0.259</v>
+      </c>
+      <c r="T45" s="3" t="n">
+        <v>0.317</v>
+      </c>
       <c r="U45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V45" s="3" t="n"/>
-      <c r="W45" s="3" t="n"/>
-      <c r="X45" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="V45" s="3" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v>0.311</v>
+      </c>
       <c r="Y45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z45" s="3" t="n"/>
-      <c r="AA45" s="3" t="n"/>
-      <c r="AB45" s="3" t="n"/>
+        <v>500</v>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v>0.093</v>
+      </c>
+      <c r="AA45" s="3" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="AB45" s="3" t="n">
+        <v>0.113</v>
+      </c>
       <c r="AC45" s="2" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="AD45" s="3" t="n">
         <v>0.303</v>
